--- a/docs/translations/translations-assamese.xlsx
+++ b/docs/translations/translations-assamese.xlsx
@@ -38,7 +38,7 @@
     <t>6. Column D says where the text appears in the app; column E has notes for that row.</t>
   </si>
   <si>
-    <t>578 texts in total.</t>
+    <t>586 texts in total.</t>
   </si>
   <si>
     <t>Key (do not change)</t>
@@ -682,6 +682,30 @@
   </si>
   <si>
     <t>Keep {{domains}}, {{competencies}} as it is: the app puts a value there.</t>
+  </si>
+  <si>
+    <t>home.wheel.hintDomainHover</t>
+  </si>
+  <si>
+    <t>Hover over a domain to see its competencies</t>
+  </si>
+  <si>
+    <t>home.wheel.hintDomainTap</t>
+  </si>
+  <si>
+    <t>Tap a domain to see its competencies</t>
+  </si>
+  <si>
+    <t>home.wheel.hintCompetencyClick</t>
+  </si>
+  <si>
+    <t>Click a competency to learn more</t>
+  </si>
+  <si>
+    <t>home.wheel.hintCompetencyTap</t>
+  </si>
+  <si>
+    <t>Tap a competency to learn more</t>
   </si>
   <si>
     <t>login.pageTitle</t>
@@ -2397,10 +2421,16 @@
     <t>childForm.back</t>
   </si>
   <si>
-    <t>childForm.name</t>
-  </si>
-  <si>
-    <t>Name</t>
+    <t>childForm.firstName</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>childForm.lastName</t>
+  </si>
+  <si>
+    <t>Last Name</t>
   </si>
   <si>
     <t>childForm.dateOfBirth</t>
@@ -2559,6 +2589,18 @@
     <t>Enter weight</t>
   </si>
   <si>
+    <t>childForm.firstNamePlaceholder</t>
+  </si>
+  <si>
+    <t>Enter first name</t>
+  </si>
+  <si>
+    <t>childForm.lastNamePlaceholder</t>
+  </si>
+  <si>
+    <t>Enter last name</t>
+  </si>
+  <si>
     <t>dashboard.title</t>
   </si>
   <si>
@@ -2785,6 +2827,12 @@
   </si>
   <si>
     <t>dashboard.export.center</t>
+  </si>
+  <si>
+    <t>dashboard.export.studentName</t>
+  </si>
+  <si>
+    <t>Student Name</t>
   </si>
   <si>
     <t>dashboard.export.sessionsDone</t>
@@ -4957,20 +5005,20 @@
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E97" s="2"/>
     </row>
@@ -4983,7 +5031,7 @@
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E98" s="2"/>
     </row>
@@ -4996,7 +5044,7 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E99" s="2"/>
     </row>
@@ -5009,20 +5057,20 @@
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E101" s="2"/>
     </row>
@@ -5035,7 +5083,7 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E102" s="2"/>
     </row>
@@ -5048,7 +5096,7 @@
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E103" s="2"/>
     </row>
@@ -5057,65 +5105,63 @@
         <v>238</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="E106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E108" s="2"/>
     </row>
@@ -5128,7 +5174,7 @@
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E109" s="2"/>
     </row>
@@ -5141,9 +5187,11 @@
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E110" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
@@ -5154,20 +5202,20 @@
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="E111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="E112" s="2"/>
     </row>
@@ -5180,7 +5228,7 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="E113" s="2"/>
     </row>
@@ -5193,7 +5241,7 @@
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="E114" s="2"/>
     </row>
@@ -5206,55 +5254,55 @@
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>260</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
@@ -5267,22 +5315,20 @@
         <v>269</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>271</v>
-      </c>
+      <c r="E120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
@@ -5292,45 +5338,43 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>271</v>
-      </c>
+      <c r="E122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="125">
@@ -5342,7 +5386,7 @@
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E125" s="2"/>
     </row>
@@ -5355,10 +5399,10 @@
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="127">
@@ -5370,7 +5414,7 @@
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E127" s="2"/>
     </row>
@@ -5383,10 +5427,10 @@
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="129">
@@ -5398,7 +5442,7 @@
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E129" s="2"/>
     </row>
@@ -5411,10 +5455,10 @@
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="131">
@@ -5426,7 +5470,7 @@
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E131" s="2"/>
     </row>
@@ -5435,14 +5479,14 @@
         <v>294</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
     </row>
     <row r="133">
@@ -5454,7 +5498,7 @@
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E133" s="2"/>
     </row>
@@ -5467,9 +5511,11 @@
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E134" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
@@ -5480,7 +5526,7 @@
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E135" s="2"/>
     </row>
@@ -5489,13 +5535,15 @@
         <v>302</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E136" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
@@ -5506,7 +5554,7 @@
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E137" s="2"/>
     </row>
@@ -5519,7 +5567,7 @@
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E138" s="2"/>
     </row>
@@ -5528,67 +5576,67 @@
         <v>308</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E143" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
@@ -5599,7 +5647,7 @@
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E144" s="2"/>
     </row>
@@ -5612,7 +5660,7 @@
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E145" s="2"/>
     </row>
@@ -5625,11 +5673,9 @@
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
@@ -5640,7 +5686,7 @@
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E147" s="2"/>
     </row>
@@ -5653,7 +5699,7 @@
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E148" s="2"/>
     </row>
@@ -5666,7 +5712,7 @@
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E149" s="2"/>
     </row>
@@ -5679,9 +5725,11 @@
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E150" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
@@ -5692,7 +5740,7 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E151" s="2"/>
     </row>
@@ -5705,7 +5753,7 @@
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E152" s="2"/>
     </row>
@@ -5714,67 +5762,67 @@
         <v>335</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E157" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
@@ -5785,7 +5833,7 @@
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E158" s="2"/>
     </row>
@@ -5798,7 +5846,7 @@
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E159" s="2"/>
     </row>
@@ -5811,11 +5859,9 @@
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
@@ -5826,7 +5872,7 @@
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E161" s="2"/>
     </row>
@@ -5839,7 +5885,7 @@
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E162" s="2"/>
     </row>
@@ -5852,7 +5898,7 @@
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E163" s="2"/>
     </row>
@@ -5865,9 +5911,11 @@
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E164" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
@@ -5878,7 +5926,7 @@
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E165" s="2"/>
     </row>
@@ -5891,7 +5939,7 @@
       </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E166" s="2"/>
     </row>
@@ -5904,11 +5952,9 @@
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
@@ -5919,7 +5965,7 @@
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E168" s="2"/>
     </row>
@@ -5932,7 +5978,7 @@
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E169" s="2"/>
     </row>
@@ -5945,7 +5991,7 @@
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E170" s="2"/>
     </row>
@@ -5958,9 +6004,11 @@
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E171" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
@@ -5971,7 +6019,7 @@
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E172" s="2"/>
     </row>
@@ -5984,7 +6032,7 @@
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E173" s="2"/>
     </row>
@@ -5997,11 +6045,9 @@
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
@@ -6012,7 +6058,7 @@
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E175" s="2"/>
     </row>
@@ -6025,7 +6071,7 @@
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E176" s="2"/>
     </row>
@@ -6038,7 +6084,7 @@
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E177" s="2"/>
     </row>
@@ -6051,9 +6097,11 @@
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E178" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
@@ -6064,7 +6112,7 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E179" s="2"/>
     </row>
@@ -6077,7 +6125,7 @@
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E180" s="2"/>
     </row>
@@ -6090,11 +6138,9 @@
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
@@ -6105,7 +6151,7 @@
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E182" s="2"/>
     </row>
@@ -6118,7 +6164,7 @@
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E183" s="2"/>
     </row>
@@ -6131,7 +6177,7 @@
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E184" s="2"/>
     </row>
@@ -6144,9 +6190,11 @@
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E185" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
@@ -6157,7 +6205,7 @@
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E186" s="2"/>
     </row>
@@ -6170,7 +6218,7 @@
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E187" s="2"/>
     </row>
@@ -6183,11 +6231,9 @@
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
@@ -6198,7 +6244,7 @@
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E189" s="2"/>
     </row>
@@ -6211,7 +6257,7 @@
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E190" s="2"/>
     </row>
@@ -6224,7 +6270,7 @@
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E191" s="2"/>
     </row>
@@ -6237,9 +6283,11 @@
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E192" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
@@ -6250,7 +6298,7 @@
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E193" s="2"/>
     </row>
@@ -6263,7 +6311,7 @@
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E194" s="2"/>
     </row>
@@ -6276,11 +6324,9 @@
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
@@ -6291,7 +6337,7 @@
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E196" s="2"/>
     </row>
@@ -6304,7 +6350,7 @@
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E197" s="2"/>
     </row>
@@ -6317,7 +6363,7 @@
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E198" s="2"/>
     </row>
@@ -6330,9 +6376,11 @@
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E199" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
@@ -6343,7 +6391,7 @@
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E200" s="2"/>
     </row>
@@ -6356,7 +6404,7 @@
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E201" s="2"/>
     </row>
@@ -6365,67 +6413,67 @@
         <v>432</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E206" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
@@ -6436,7 +6484,7 @@
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E207" s="2"/>
     </row>
@@ -6449,7 +6497,7 @@
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E208" s="2"/>
     </row>
@@ -6462,11 +6510,9 @@
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
@@ -6477,7 +6523,7 @@
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E210" s="2"/>
     </row>
@@ -6490,7 +6536,7 @@
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E211" s="2"/>
     </row>
@@ -6503,7 +6549,7 @@
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E212" s="2"/>
     </row>
@@ -6516,9 +6562,11 @@
       </c>
       <c r="C213" s="2"/>
       <c r="D213" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E213" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
@@ -6529,7 +6577,7 @@
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E214" s="2"/>
     </row>
@@ -6542,7 +6590,7 @@
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E215" s="2"/>
     </row>
@@ -6555,11 +6603,9 @@
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
@@ -6570,7 +6616,7 @@
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E217" s="2"/>
     </row>
@@ -6583,7 +6629,7 @@
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E218" s="2"/>
     </row>
@@ -6596,7 +6642,7 @@
       </c>
       <c r="C219" s="2"/>
       <c r="D219" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E219" s="2"/>
     </row>
@@ -6609,9 +6655,11 @@
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E220" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
@@ -6622,7 +6670,7 @@
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E221" s="2"/>
     </row>
@@ -6635,7 +6683,7 @@
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E222" s="2"/>
     </row>
@@ -6644,67 +6692,67 @@
         <v>473</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E227" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
@@ -6715,7 +6763,7 @@
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E228" s="2"/>
     </row>
@@ -6728,7 +6776,7 @@
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E229" s="2"/>
     </row>
@@ -6741,11 +6789,9 @@
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
@@ -6756,7 +6802,7 @@
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E231" s="2"/>
     </row>
@@ -6769,7 +6815,7 @@
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E232" s="2"/>
     </row>
@@ -6782,7 +6828,7 @@
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E233" s="2"/>
     </row>
@@ -6795,9 +6841,11 @@
       </c>
       <c r="C234" s="2"/>
       <c r="D234" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E234" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
@@ -6808,7 +6856,7 @@
       </c>
       <c r="C235" s="2"/>
       <c r="D235" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E235" s="2"/>
     </row>
@@ -6821,7 +6869,7 @@
       </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E236" s="2"/>
     </row>
@@ -6834,11 +6882,9 @@
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
@@ -6849,7 +6895,7 @@
       </c>
       <c r="C238" s="2"/>
       <c r="D238" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E238" s="2"/>
     </row>
@@ -6862,7 +6908,7 @@
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E239" s="2"/>
     </row>
@@ -6875,7 +6921,7 @@
       </c>
       <c r="C240" s="2"/>
       <c r="D240" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E240" s="2"/>
     </row>
@@ -6888,9 +6934,11 @@
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E241" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
@@ -6901,7 +6949,7 @@
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E242" s="2"/>
     </row>
@@ -6914,7 +6962,7 @@
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E243" s="2"/>
     </row>
@@ -6923,67 +6971,67 @@
         <v>514</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="E244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E248" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
@@ -6994,7 +7042,7 @@
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E249" s="2"/>
     </row>
@@ -7007,59 +7055,59 @@
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2" t="s">
-        <v>527</v>
+        <v>276</v>
       </c>
       <c r="E250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" s="2" t="s">
-        <v>527</v>
+        <v>276</v>
       </c>
       <c r="E251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" s="2" t="s">
-        <v>527</v>
+        <v>276</v>
       </c>
       <c r="E252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>533</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" s="2" t="s">
-        <v>527</v>
+        <v>276</v>
       </c>
       <c r="E253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E254" s="2"/>
     </row>
@@ -7072,7 +7120,7 @@
       </c>
       <c r="C255" s="2"/>
       <c r="D255" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E255" s="2"/>
     </row>
@@ -7085,7 +7133,7 @@
       </c>
       <c r="C256" s="2"/>
       <c r="D256" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E256" s="2"/>
     </row>
@@ -7098,7 +7146,7 @@
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E257" s="2"/>
     </row>
@@ -7111,33 +7159,33 @@
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2" t="s">
-        <v>27</v>
+        <v>535</v>
       </c>
       <c r="E260" s="2"/>
     </row>
@@ -7150,7 +7198,7 @@
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2" t="s">
-        <v>27</v>
+        <v>535</v>
       </c>
       <c r="E261" s="2"/>
     </row>
@@ -7163,33 +7211,29 @@
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="E262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="E263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>555</v>
+        <v>27</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2" t="s">
@@ -7208,72 +7252,76 @@
       <c r="D265" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E265" s="2" t="s">
-        <v>558</v>
-      </c>
+      <c r="E265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E266" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E267" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" s="2" t="s">
-        <v>561</v>
+        <v>27</v>
       </c>
       <c r="E268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="E269" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" s="2" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="E270" s="2"/>
     </row>
@@ -7286,7 +7334,7 @@
       </c>
       <c r="C271" s="2"/>
       <c r="D271" s="2" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="E271" s="2"/>
     </row>
@@ -7299,102 +7347,102 @@
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>581</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="E275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B278" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E279" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
@@ -7405,7 +7453,7 @@
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E280" s="2"/>
     </row>
@@ -7418,7 +7466,7 @@
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E281" s="2"/>
     </row>
@@ -7431,7 +7479,7 @@
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E282" s="2"/>
     </row>
@@ -7444,7 +7492,7 @@
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E283" s="2"/>
     </row>
@@ -7457,7 +7505,7 @@
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="2" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="E284" s="2"/>
     </row>
@@ -7470,74 +7518,74 @@
       </c>
       <c r="C285" s="2"/>
       <c r="D285" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="E285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
         <v>602</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="E286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" s="2" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="E287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E289" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E290" s="2"/>
     </row>
@@ -7550,7 +7598,7 @@
       </c>
       <c r="C291" s="2"/>
       <c r="D291" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2"/>
     </row>
@@ -7563,7 +7611,7 @@
       </c>
       <c r="C292" s="2"/>
       <c r="D292" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E292" s="2"/>
     </row>
@@ -7576,7 +7624,7 @@
       </c>
       <c r="C293" s="2"/>
       <c r="D293" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E293" s="2"/>
     </row>
@@ -7589,7 +7637,7 @@
       </c>
       <c r="C294" s="2"/>
       <c r="D294" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E294" s="2"/>
     </row>
@@ -7602,7 +7650,7 @@
       </c>
       <c r="C295" s="2"/>
       <c r="D295" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E295" s="2"/>
     </row>
@@ -7615,7 +7663,7 @@
       </c>
       <c r="C296" s="2"/>
       <c r="D296" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E296" s="2"/>
     </row>
@@ -7628,7 +7676,7 @@
       </c>
       <c r="C297" s="2"/>
       <c r="D297" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E297" s="2"/>
     </row>
@@ -7641,70 +7689,62 @@
       </c>
       <c r="C298" s="2"/>
       <c r="D298" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>627</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>627</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>627</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="C301" s="2"/>
       <c r="D301" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>627</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="C302" s="2"/>
       <c r="D302" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>581</v>
+        <v>635</v>
       </c>
     </row>
     <row r="303">
@@ -7716,9 +7756,11 @@
       </c>
       <c r="C303" s="2"/>
       <c r="D303" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E303" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
@@ -7729,68 +7771,68 @@
       </c>
       <c r="C304" s="2"/>
       <c r="D304" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="C305" s="2"/>
       <c r="D305" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>581</v>
+        <v>635</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B306" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B307" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B308" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>92</v>
+        <v>648</v>
       </c>
     </row>
     <row r="309">
@@ -7802,91 +7844,93 @@
       </c>
       <c r="C309" s="2"/>
       <c r="D309" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E310" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E313" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
         <v>660</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>591</v>
+        <v>661</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>172</v>
@@ -7894,14 +7938,14 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>175</v>
@@ -7909,33 +7953,29 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>667</v>
+        <v>599</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>668</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
@@ -7946,48 +7986,56 @@
       </c>
       <c r="C319" s="2"/>
       <c r="D319" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E319" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
         <v>671</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C320" s="2"/>
       <c r="D320" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E320" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E321" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B322" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="C322" s="2"/>
       <c r="D322" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E322" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
@@ -7998,7 +8046,7 @@
       </c>
       <c r="C323" s="2"/>
       <c r="D323" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E323" s="2"/>
     </row>
@@ -8011,63 +8059,63 @@
       </c>
       <c r="C324" s="2"/>
       <c r="D324" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>681</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B325" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="C325" s="2"/>
       <c r="D325" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B327" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="C327" s="2"/>
       <c r="D327" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E328" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
@@ -8078,65 +8126,63 @@
       </c>
       <c r="C329" s="2"/>
       <c r="D329" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E329" s="2" t="s">
-        <v>692</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="C330" s="2"/>
       <c r="D330" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E330" s="2" t="s">
-        <v>695</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C332" s="2"/>
       <c r="D332" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>77</v>
+        <v>699</v>
       </c>
       <c r="C333" s="2"/>
       <c r="D333" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E333" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
@@ -8147,7 +8193,7 @@
       </c>
       <c r="C334" s="2"/>
       <c r="D334" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>703</v>
@@ -8158,15 +8204,13 @@
         <v>704</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C335" s="2"/>
       <c r="D335" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E335" s="2" t="s">
-        <v>705</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
@@ -8177,67 +8221,67 @@
       </c>
       <c r="C336" s="2"/>
       <c r="D336" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E336" s="2" t="s">
-        <v>708</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>710</v>
+        <v>77</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E337" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C338" s="2"/>
       <c r="D338" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>175</v>
+        <v>711</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C339" s="2"/>
       <c r="D339" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E339" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="C340" s="2"/>
       <c r="D340" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E340" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>716</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
@@ -8248,7 +8292,7 @@
       </c>
       <c r="C341" s="2"/>
       <c r="D341" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>172</v>
@@ -8263,7 +8307,7 @@
       </c>
       <c r="C342" s="2"/>
       <c r="D342" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>175</v>
@@ -8278,7 +8322,7 @@
       </c>
       <c r="C343" s="2"/>
       <c r="D343" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E343" s="2"/>
     </row>
@@ -8291,7 +8335,7 @@
       </c>
       <c r="C344" s="2"/>
       <c r="D344" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E344" s="2"/>
     </row>
@@ -8304,9 +8348,11 @@
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E345" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
@@ -8317,10 +8363,10 @@
       </c>
       <c r="C346" s="2"/>
       <c r="D346" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
     </row>
     <row r="347">
@@ -8332,7 +8378,7 @@
       </c>
       <c r="C347" s="2"/>
       <c r="D347" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E347" s="2"/>
     </row>
@@ -8345,7 +8391,7 @@
       </c>
       <c r="C348" s="2"/>
       <c r="D348" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E348" s="2"/>
     </row>
@@ -8358,7 +8404,7 @@
       </c>
       <c r="C349" s="2"/>
       <c r="D349" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E349" s="2"/>
     </row>
@@ -8371,9 +8417,11 @@
       </c>
       <c r="C350" s="2"/>
       <c r="D350" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E350" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
@@ -8384,7 +8432,7 @@
       </c>
       <c r="C351" s="2"/>
       <c r="D351" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E351" s="2"/>
     </row>
@@ -8397,63 +8445,59 @@
       </c>
       <c r="C352" s="2"/>
       <c r="D352" s="2" t="s">
-        <v>741</v>
+        <v>607</v>
       </c>
       <c r="E352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B353" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="C353" s="2"/>
       <c r="D353" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E353" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B354" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>745</v>
       </c>
       <c r="C354" s="2"/>
       <c r="D354" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E354" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="E354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B355" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>747</v>
       </c>
       <c r="C355" s="2"/>
       <c r="D355" s="2" t="s">
-        <v>741</v>
+        <v>607</v>
       </c>
       <c r="E355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B356" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="C356" s="2"/>
       <c r="D356" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E356" s="2"/>
     </row>
@@ -8466,9 +8510,11 @@
       </c>
       <c r="C357" s="2"/>
       <c r="D357" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E357" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
@@ -8479,9 +8525,11 @@
       </c>
       <c r="C358" s="2"/>
       <c r="D358" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E358" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
@@ -8492,7 +8540,7 @@
       </c>
       <c r="C359" s="2"/>
       <c r="D359" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E359" s="2"/>
     </row>
@@ -8505,7 +8553,7 @@
       </c>
       <c r="C360" s="2"/>
       <c r="D360" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E360" s="2"/>
     </row>
@@ -8514,28 +8562,26 @@
         <v>758</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>653</v>
+        <v>759</v>
       </c>
       <c r="C361" s="2"/>
       <c r="D361" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>761</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="E362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
@@ -8546,11 +8592,9 @@
       </c>
       <c r="C363" s="2"/>
       <c r="D363" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E363" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="E363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
@@ -8561,38 +8605,36 @@
       </c>
       <c r="C364" s="2"/>
       <c r="D364" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E364" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="E364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
         <v>766</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>767</v>
+        <v>661</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B366" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="C366" s="2"/>
       <c r="D366" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>92</v>
+        <v>769</v>
       </c>
     </row>
     <row r="367">
@@ -8604,9 +8646,11 @@
       </c>
       <c r="C367" s="2"/>
       <c r="D367" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E367" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
@@ -8617,7 +8661,7 @@
       </c>
       <c r="C368" s="2"/>
       <c r="D368" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>92</v>
@@ -8632,7 +8676,7 @@
       </c>
       <c r="C369" s="2"/>
       <c r="D369" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E369" s="2"/>
     </row>
@@ -8645,9 +8689,11 @@
       </c>
       <c r="C370" s="2"/>
       <c r="D370" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E370" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
@@ -8658,11 +8704,9 @@
       </c>
       <c r="C371" s="2"/>
       <c r="D371" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E371" s="2" t="s">
-        <v>705</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="E371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
@@ -8673,33 +8717,35 @@
       </c>
       <c r="C372" s="2"/>
       <c r="D372" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E372" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="B373" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="C373" s="2"/>
       <c r="D373" s="2" t="s">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="E373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B374" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C374" s="2"/>
       <c r="D374" s="2" t="s">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="E374" s="2"/>
     </row>
@@ -8712,9 +8758,11 @@
       </c>
       <c r="C375" s="2"/>
       <c r="D375" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E375" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
@@ -8725,74 +8773,72 @@
       </c>
       <c r="C376" s="2"/>
       <c r="D376" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C377" s="2"/>
       <c r="D377" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E377" s="2" t="s">
-        <v>792</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="E377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
         <v>793</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>794</v>
+        <v>31</v>
       </c>
       <c r="C378" s="2"/>
       <c r="D378" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B379" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="B379" s="2" t="s">
-        <v>796</v>
       </c>
       <c r="C379" s="2"/>
       <c r="D379" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E379" s="2"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B380" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="B380" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="C380" s="2"/>
       <c r="D380" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B381" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B381" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="C381" s="2"/>
       <c r="D381" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E381" s="2"/>
     </row>
@@ -8801,89 +8847,91 @@
         <v>800</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>678</v>
+        <v>801</v>
       </c>
       <c r="C382" s="2"/>
       <c r="D382" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E382" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>751</v>
+        <v>804</v>
       </c>
       <c r="C383" s="2"/>
       <c r="D383" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C384" s="2"/>
       <c r="D384" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C385" s="2"/>
       <c r="D385" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>807</v>
+        <v>684</v>
       </c>
       <c r="C386" s="2"/>
       <c r="D386" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>809</v>
+        <v>686</v>
       </c>
       <c r="C387" s="2"/>
       <c r="D387" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>811</v>
+        <v>759</v>
       </c>
       <c r="C388" s="2"/>
       <c r="D388" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E388" s="2"/>
     </row>
@@ -8896,7 +8944,7 @@
       </c>
       <c r="C389" s="2"/>
       <c r="D389" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E389" s="2"/>
     </row>
@@ -8909,11 +8957,9 @@
       </c>
       <c r="C390" s="2"/>
       <c r="D390" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E390" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="E390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
@@ -8924,11 +8970,9 @@
       </c>
       <c r="C391" s="2"/>
       <c r="D391" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E391" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="E391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
@@ -8939,7 +8983,7 @@
       </c>
       <c r="C392" s="2"/>
       <c r="D392" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E392" s="2"/>
     </row>
@@ -8952,7 +8996,7 @@
       </c>
       <c r="C393" s="2"/>
       <c r="D393" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E393" s="2"/>
     </row>
@@ -8965,7 +9009,7 @@
       </c>
       <c r="C394" s="2"/>
       <c r="D394" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E394" s="2"/>
     </row>
@@ -8978,7 +9022,7 @@
       </c>
       <c r="C395" s="2"/>
       <c r="D395" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>92</v>
@@ -8993,9 +9037,11 @@
       </c>
       <c r="C396" s="2"/>
       <c r="D396" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E396" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
@@ -9006,11 +9052,9 @@
       </c>
       <c r="C397" s="2"/>
       <c r="D397" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E397" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="E397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
@@ -9021,7 +9065,7 @@
       </c>
       <c r="C398" s="2"/>
       <c r="D398" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E398" s="2"/>
     </row>
@@ -9034,7 +9078,7 @@
       </c>
       <c r="C399" s="2"/>
       <c r="D399" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E399" s="2"/>
     </row>
@@ -9047,9 +9091,11 @@
       </c>
       <c r="C400" s="2"/>
       <c r="D400" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E400" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
@@ -9060,7 +9106,7 @@
       </c>
       <c r="C401" s="2"/>
       <c r="D401" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="E401" s="2"/>
     </row>
@@ -9073,107 +9119,109 @@
       </c>
       <c r="C402" s="2"/>
       <c r="D402" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="E402" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="E402" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
         <v>840</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>33</v>
+        <v>841</v>
       </c>
       <c r="C403" s="2"/>
       <c r="D403" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C405" s="2"/>
       <c r="D405" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C406" s="2"/>
       <c r="D406" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C407" s="2"/>
       <c r="D407" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="2" t="s">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="E409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C410" s="2"/>
       <c r="D410" s="2" t="s">
@@ -9183,10 +9231,10 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C411" s="2"/>
       <c r="D411" s="2" t="s">
@@ -9196,10 +9244,10 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C412" s="2"/>
       <c r="D412" s="2" t="s">
@@ -9209,70 +9257,62 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C413" s="2"/>
       <c r="D413" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E413" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="E413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C414" s="2"/>
       <c r="D414" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E414" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="E414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C415" s="2"/>
       <c r="D415" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E415" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="E415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C416" s="2"/>
       <c r="D416" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E416" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="E416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>867</v>
+        <v>31</v>
       </c>
       <c r="C417" s="2"/>
       <c r="D417" s="2" t="s">
@@ -9291,16 +9331,14 @@
       <c r="D418" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E418" s="2" t="s">
-        <v>870</v>
-      </c>
+      <c r="E418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B419" s="2" t="s">
         <v>871</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>872</v>
       </c>
       <c r="C419" s="2"/>
       <c r="D419" s="2" t="s">
@@ -9310,64 +9348,70 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B420" s="2" t="s">
         <v>873</v>
-      </c>
-      <c r="B420" s="2" t="s">
-        <v>874</v>
       </c>
       <c r="C420" s="2"/>
       <c r="D420" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>875</v>
+        <v>172</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C421" s="2"/>
       <c r="D421" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E421" s="2"/>
+      <c r="E421" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C422" s="2"/>
       <c r="D422" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E422" s="2"/>
+      <c r="E422" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C423" s="2"/>
       <c r="D423" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E423" s="2"/>
+      <c r="E423" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C424" s="2"/>
       <c r="D424" s="2" t="s">
@@ -9377,23 +9421,25 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C425" s="2"/>
       <c r="D425" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E425" s="2"/>
+      <c r="E425" s="2" t="s">
+        <v>884</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B426" s="2" t="s">
         <v>886</v>
-      </c>
-      <c r="B426" s="2" t="s">
-        <v>887</v>
       </c>
       <c r="C426" s="2"/>
       <c r="D426" s="2" t="s">
@@ -9403,16 +9449,18 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B427" s="2" t="s">
         <v>888</v>
-      </c>
-      <c r="B427" s="2" t="s">
-        <v>889</v>
       </c>
       <c r="C427" s="2"/>
       <c r="D427" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E427" s="2"/>
+      <c r="E427" s="2" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
@@ -9432,7 +9480,7 @@
         <v>892</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>646</v>
+        <v>893</v>
       </c>
       <c r="C429" s="2"/>
       <c r="D429" s="2" t="s">
@@ -9442,10 +9490,10 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C430" s="2"/>
       <c r="D430" s="2" t="s">
@@ -9455,18 +9503,16 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C431" s="2"/>
       <c r="D431" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E431" s="2" t="s">
-        <v>897</v>
-      </c>
+      <c r="E431" s="2"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
@@ -9512,7 +9558,7 @@
         <v>904</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>573</v>
+        <v>905</v>
       </c>
       <c r="C435" s="2"/>
       <c r="D435" s="2" t="s">
@@ -9522,10 +9568,10 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>877</v>
+        <v>654</v>
       </c>
       <c r="C436" s="2"/>
       <c r="D436" s="2" t="s">
@@ -9535,10 +9581,10 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C437" s="2"/>
       <c r="D437" s="2" t="s">
@@ -9548,23 +9594,25 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>881</v>
+        <v>910</v>
       </c>
       <c r="C438" s="2"/>
       <c r="D438" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E438" s="2"/>
+      <c r="E438" s="2" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C439" s="2"/>
       <c r="D439" s="2" t="s">
@@ -9574,10 +9622,10 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C440" s="2"/>
       <c r="D440" s="2" t="s">
@@ -9587,10 +9635,10 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C441" s="2"/>
       <c r="D441" s="2" t="s">
@@ -9600,10 +9648,10 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>83</v>
+        <v>581</v>
       </c>
       <c r="C442" s="2"/>
       <c r="D442" s="2" t="s">
@@ -9613,10 +9661,10 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="C443" s="2"/>
       <c r="D443" s="2" t="s">
@@ -9626,10 +9674,10 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C444" s="2"/>
       <c r="D444" s="2" t="s">
@@ -9639,10 +9687,10 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>184</v>
+        <v>895</v>
       </c>
       <c r="C445" s="2"/>
       <c r="D445" s="2" t="s">
@@ -9652,10 +9700,10 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="C446" s="2"/>
       <c r="D446" s="2" t="s">
@@ -9665,10 +9713,10 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C447" s="2"/>
       <c r="D447" s="2" t="s">
@@ -9678,10 +9726,10 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>31</v>
+        <v>928</v>
       </c>
       <c r="C448" s="2"/>
       <c r="D448" s="2" t="s">
@@ -9691,10 +9739,10 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>926</v>
+        <v>83</v>
       </c>
       <c r="C449" s="2"/>
       <c r="D449" s="2" t="s">
@@ -9704,10 +9752,10 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C450" s="2"/>
       <c r="D450" s="2" t="s">
@@ -9717,10 +9765,10 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>930</v>
+        <v>881</v>
       </c>
       <c r="C451" s="2"/>
       <c r="D451" s="2" t="s">
@@ -9730,10 +9778,10 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C452" s="2"/>
       <c r="D452" s="2" t="s">
@@ -9743,10 +9791,10 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>934</v>
+        <v>184</v>
       </c>
       <c r="C453" s="2"/>
       <c r="D453" s="2" t="s">
@@ -9756,10 +9804,10 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C454" s="2"/>
       <c r="D454" s="2" t="s">
@@ -9769,10 +9817,10 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C455" s="2"/>
       <c r="D455" s="2" t="s">
@@ -9782,10 +9830,10 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>940</v>
+        <v>31</v>
       </c>
       <c r="C456" s="2"/>
       <c r="D456" s="2" t="s">
@@ -9837,7 +9885,7 @@
         <v>947</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>846</v>
+        <v>948</v>
       </c>
       <c r="C460" s="2"/>
       <c r="D460" s="2" t="s">
@@ -9847,10 +9895,10 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="C461" s="2"/>
       <c r="D461" s="2" t="s">
@@ -9860,10 +9908,10 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>31</v>
+        <v>952</v>
       </c>
       <c r="C462" s="2"/>
       <c r="D462" s="2" t="s">
@@ -9873,10 +9921,10 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C463" s="2"/>
       <c r="D463" s="2" t="s">
@@ -9886,10 +9934,10 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C464" s="2"/>
       <c r="D464" s="2" t="s">
@@ -9899,40 +9947,36 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>644</v>
+        <v>958</v>
       </c>
       <c r="C465" s="2"/>
       <c r="D465" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E465" s="2" t="s">
-        <v>581</v>
-      </c>
+      <c r="E465" s="2"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C466" s="2"/>
       <c r="D466" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E466" s="2" t="s">
-        <v>957</v>
-      </c>
+      <c r="E466" s="2"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C467" s="2"/>
       <c r="D467" s="2" t="s">
@@ -9942,48 +9986,42 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>961</v>
+        <v>860</v>
       </c>
       <c r="C468" s="2"/>
       <c r="D468" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E468" s="2" t="s">
-        <v>627</v>
-      </c>
+      <c r="E468" s="2"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="C469" s="2"/>
       <c r="D469" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E469" s="2" t="s">
-        <v>627</v>
-      </c>
+      <c r="E469" s="2"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>965</v>
+        <v>31</v>
       </c>
       <c r="C470" s="2"/>
       <c r="D470" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E470" s="2" t="s">
-        <v>627</v>
-      </c>
+      <c r="E470" s="2"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
@@ -10016,26 +10054,30 @@
         <v>970</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>971</v>
+        <v>652</v>
       </c>
       <c r="C473" s="2"/>
       <c r="D473" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E473" s="2"/>
+      <c r="E473" s="2" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B474" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="B474" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="C474" s="2"/>
       <c r="D474" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E474" s="2"/>
+      <c r="E474" s="2" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
@@ -10048,70 +10090,72 @@
       <c r="D475" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E475" s="2" t="s">
-        <v>976</v>
-      </c>
+      <c r="E475" s="2"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B476" s="2" t="s">
         <v>977</v>
-      </c>
-      <c r="B476" s="2" t="s">
-        <v>978</v>
       </c>
       <c r="C476" s="2"/>
       <c r="D476" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E476" s="2"/>
+      <c r="E476" s="2" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="B477" s="2" t="s">
         <v>979</v>
-      </c>
-      <c r="B477" s="2" t="s">
-        <v>980</v>
       </c>
       <c r="C477" s="2"/>
       <c r="D477" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E477" s="2"/>
+      <c r="E477" s="2" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B478" s="2" t="s">
         <v>981</v>
-      </c>
-      <c r="B478" s="2" t="s">
-        <v>982</v>
       </c>
       <c r="C478" s="2"/>
       <c r="D478" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E478" s="2"/>
+      <c r="E478" s="2" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B479" s="2" t="s">
         <v>983</v>
-      </c>
-      <c r="B479" s="2" t="s">
-        <v>984</v>
       </c>
       <c r="C479" s="2"/>
       <c r="D479" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E479" s="2" t="s">
-        <v>985</v>
-      </c>
+      <c r="E479" s="2"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C480" s="2"/>
       <c r="D480" s="2" t="s">
@@ -10121,10 +10165,10 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>653</v>
+        <v>987</v>
       </c>
       <c r="C481" s="2"/>
       <c r="D481" s="2" t="s">
@@ -10134,10 +10178,10 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B482" s="2" t="s">
         <v>989</v>
-      </c>
-      <c r="B482" s="2" t="s">
-        <v>990</v>
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="2" t="s">
@@ -10147,16 +10191,18 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B483" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="B483" s="2" t="s">
-        <v>992</v>
       </c>
       <c r="C483" s="2"/>
       <c r="D483" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E483" s="2"/>
+      <c r="E483" s="2" t="s">
+        <v>992</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
@@ -10195,91 +10241,81 @@
       <c r="D486" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E486" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="E486" s="2"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
         <v>999</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C487" s="2"/>
       <c r="D487" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>175</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C488" s="2"/>
       <c r="D488" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E488" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="E488" s="2"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1001</v>
+        <v>661</v>
       </c>
       <c r="C489" s="2"/>
       <c r="D489" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E489" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="E489" s="2"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C490" s="2"/>
       <c r="D490" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E490" s="2" t="s">
-        <v>172</v>
-      </c>
+      <c r="E490" s="2"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C491" s="2"/>
       <c r="D491" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E491" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="E491" s="2"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C492" s="2"/>
       <c r="D492" s="2" t="s">
@@ -10289,10 +10325,10 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C493" s="2"/>
       <c r="D493" s="2" t="s">
@@ -10302,81 +10338,93 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>646</v>
+        <v>1014</v>
       </c>
       <c r="C494" s="2"/>
       <c r="D494" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E494" s="2"/>
+      <c r="E494" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C495" s="2"/>
       <c r="D495" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E495" s="2"/>
+      <c r="E495" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C496" s="2"/>
       <c r="D496" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E496" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="E496" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>1017</v>
       </c>
       <c r="C497" s="2"/>
       <c r="D497" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E497" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="E497" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C498" s="2"/>
       <c r="D498" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E498" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="E498" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B499" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="B499" s="2" t="s">
-        <v>1021</v>
       </c>
       <c r="C499" s="2"/>
       <c r="D499" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E499" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="E499" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
@@ -10387,7 +10435,7 @@
       </c>
       <c r="C500" s="2"/>
       <c r="D500" s="2" t="s">
-        <v>1015</v>
+        <v>33</v>
       </c>
       <c r="E500" s="2"/>
     </row>
@@ -10400,7 +10448,7 @@
       </c>
       <c r="C501" s="2"/>
       <c r="D501" s="2" t="s">
-        <v>1015</v>
+        <v>33</v>
       </c>
       <c r="E501" s="2"/>
     </row>
@@ -10409,37 +10457,37 @@
         <v>1026</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1027</v>
+        <v>654</v>
       </c>
       <c r="C502" s="2"/>
       <c r="D502" s="2" t="s">
-        <v>1015</v>
+        <v>33</v>
       </c>
       <c r="E502" s="2"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B503" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="B503" s="2" t="s">
-        <v>1029</v>
       </c>
       <c r="C503" s="2"/>
       <c r="D503" s="2" t="s">
-        <v>1015</v>
+        <v>33</v>
       </c>
       <c r="E503" s="2"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B504" s="2" t="s">
         <v>1030</v>
-      </c>
-      <c r="B504" s="2" t="s">
-        <v>1031</v>
       </c>
       <c r="C504" s="2"/>
       <c r="D504" s="2" t="s">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="E504" s="2"/>
     </row>
@@ -10452,7 +10500,7 @@
       </c>
       <c r="C505" s="2"/>
       <c r="D505" s="2" t="s">
-        <v>1015</v>
+        <v>1031</v>
       </c>
       <c r="E505" s="2"/>
     </row>
@@ -10461,11 +10509,11 @@
         <v>1034</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>33</v>
+        <v>1035</v>
       </c>
       <c r="C506" s="2"/>
       <c r="D506" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E506" s="2"/>
     </row>
@@ -10478,11 +10526,9 @@
       </c>
       <c r="C507" s="2"/>
       <c r="D507" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E507" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1031</v>
+      </c>
+      <c r="E507" s="2"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
@@ -10493,7 +10539,7 @@
       </c>
       <c r="C508" s="2"/>
       <c r="D508" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E508" s="2"/>
     </row>
@@ -10506,7 +10552,7 @@
       </c>
       <c r="C509" s="2"/>
       <c r="D509" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E509" s="2"/>
     </row>
@@ -10519,7 +10565,7 @@
       </c>
       <c r="C510" s="2"/>
       <c r="D510" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E510" s="2"/>
     </row>
@@ -10532,7 +10578,7 @@
       </c>
       <c r="C511" s="2"/>
       <c r="D511" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E511" s="2"/>
     </row>
@@ -10545,7 +10591,7 @@
       </c>
       <c r="C512" s="2"/>
       <c r="D512" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E512" s="2"/>
     </row>
@@ -10554,11 +10600,11 @@
         <v>1048</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>33</v>
+        <v>1049</v>
       </c>
       <c r="C513" s="2"/>
       <c r="D513" s="2" t="s">
-        <v>1049</v>
+        <v>1031</v>
       </c>
       <c r="E513" s="2"/>
     </row>
@@ -10567,199 +10613,197 @@
         <v>1050</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1037</v>
+        <v>33</v>
       </c>
       <c r="C514" s="2"/>
       <c r="D514" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E514" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1051</v>
+      </c>
+      <c r="E514" s="2"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>36</v>
+        <v>1053</v>
       </c>
       <c r="C515" s="2"/>
       <c r="D515" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E515" s="2"/>
+        <v>1051</v>
+      </c>
+      <c r="E515" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C516" s="2"/>
       <c r="D516" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E516" s="2"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>31</v>
+        <v>1057</v>
       </c>
       <c r="C517" s="2"/>
       <c r="D517" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E517" s="2"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="C518" s="2"/>
       <c r="D518" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E518" s="2"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="C519" s="2"/>
       <c r="D519" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E519" s="2"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="C520" s="2"/>
       <c r="D520" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E520" s="2"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1061</v>
+        <v>33</v>
       </c>
       <c r="C521" s="2"/>
       <c r="D521" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E521" s="2"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="C522" s="2"/>
       <c r="D522" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E522" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1065</v>
+        <v>36</v>
       </c>
       <c r="C523" s="2"/>
       <c r="D523" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E523" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E523" s="2"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C524" s="2"/>
       <c r="D524" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E524" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E524" s="2"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1069</v>
+        <v>31</v>
       </c>
       <c r="C525" s="2"/>
       <c r="D525" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E525" s="2"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C526" s="2"/>
       <c r="D526" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E526" s="2"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C527" s="2"/>
       <c r="D527" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E527" s="2"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
       <c r="C528" s="2"/>
       <c r="D528" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E528" s="2"/>
     </row>
@@ -10772,7 +10816,7 @@
       </c>
       <c r="C529" s="2"/>
       <c r="D529" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E529" s="2"/>
     </row>
@@ -10785,7 +10829,7 @@
       </c>
       <c r="C530" s="2"/>
       <c r="D530" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E530" s="2"/>
     </row>
@@ -10798,9 +10842,11 @@
       </c>
       <c r="C531" s="2"/>
       <c r="D531" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E531" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E531" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
@@ -10811,309 +10857,307 @@
       </c>
       <c r="C532" s="2"/>
       <c r="D532" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E532" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E532" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
         <v>1084</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>763</v>
+        <v>1085</v>
       </c>
       <c r="C533" s="2"/>
       <c r="D533" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E533" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E533" s="2"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>765</v>
+        <v>1087</v>
       </c>
       <c r="C534" s="2"/>
       <c r="D534" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E534" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E534" s="2"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C535" s="2"/>
       <c r="D535" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E535" s="2"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>769</v>
+        <v>1091</v>
       </c>
       <c r="C536" s="2"/>
       <c r="D536" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E536" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E536" s="2"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>771</v>
+        <v>1093</v>
       </c>
       <c r="C537" s="2"/>
       <c r="D537" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E537" s="2"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="C538" s="2"/>
       <c r="D538" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E538" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E538" s="2"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="C539" s="2"/>
       <c r="D539" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E539" s="2"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>229</v>
+        <v>1099</v>
       </c>
       <c r="C540" s="2"/>
       <c r="D540" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E540" s="2"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1096</v>
+        <v>771</v>
       </c>
       <c r="C541" s="2"/>
       <c r="D541" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E541" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E541" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1098</v>
+        <v>773</v>
       </c>
       <c r="C542" s="2"/>
       <c r="D542" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E542" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>794</v>
+        <v>1103</v>
       </c>
       <c r="C543" s="2"/>
       <c r="D543" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E543" s="2"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1101</v>
+        <v>777</v>
       </c>
       <c r="C544" s="2"/>
       <c r="D544" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E544" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E544" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1103</v>
+        <v>779</v>
       </c>
       <c r="C545" s="2"/>
       <c r="D545" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E545" s="2"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>779</v>
+        <v>1107</v>
       </c>
       <c r="C546" s="2"/>
       <c r="D546" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>705</v>
+        <v>92</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C547" s="2"/>
       <c r="D547" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E547" s="2"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1108</v>
+        <v>237</v>
       </c>
       <c r="C548" s="2"/>
       <c r="D548" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E548" s="2"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C549" s="2"/>
       <c r="D549" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E549" s="2"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C550" s="2"/>
       <c r="D550" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E550" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E550" s="2"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1114</v>
+        <v>804</v>
       </c>
       <c r="C551" s="2"/>
       <c r="D551" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E551" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E551" s="2"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C552" s="2"/>
       <c r="D552" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E552" s="2"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C553" s="2"/>
       <c r="D553" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E553" s="2"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1120</v>
+        <v>787</v>
       </c>
       <c r="C554" s="2"/>
       <c r="D554" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E554" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E554" s="2" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
@@ -11124,7 +11168,7 @@
       </c>
       <c r="C555" s="2"/>
       <c r="D555" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E555" s="2"/>
     </row>
@@ -11137,7 +11181,7 @@
       </c>
       <c r="C556" s="2"/>
       <c r="D556" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E556" s="2"/>
     </row>
@@ -11150,7 +11194,7 @@
       </c>
       <c r="C557" s="2"/>
       <c r="D557" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E557" s="2"/>
     </row>
@@ -11163,10 +11207,10 @@
       </c>
       <c r="C558" s="2"/>
       <c r="D558" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
     </row>
     <row r="559">
@@ -11178,10 +11222,10 @@
       </c>
       <c r="C559" s="2"/>
       <c r="D559" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
     </row>
     <row r="560">
@@ -11193,7 +11237,7 @@
       </c>
       <c r="C560" s="2"/>
       <c r="D560" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E560" s="2"/>
     </row>
@@ -11206,7 +11250,7 @@
       </c>
       <c r="C561" s="2"/>
       <c r="D561" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E561" s="2"/>
     </row>
@@ -11219,7 +11263,7 @@
       </c>
       <c r="C562" s="2"/>
       <c r="D562" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E562" s="2"/>
     </row>
@@ -11232,7 +11276,7 @@
       </c>
       <c r="C563" s="2"/>
       <c r="D563" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E563" s="2"/>
     </row>
@@ -11245,7 +11289,7 @@
       </c>
       <c r="C564" s="2"/>
       <c r="D564" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E564" s="2"/>
     </row>
@@ -11258,7 +11302,7 @@
       </c>
       <c r="C565" s="2"/>
       <c r="D565" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E565" s="2"/>
     </row>
@@ -11267,121 +11311,119 @@
         <v>1143</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>763</v>
+        <v>1144</v>
       </c>
       <c r="C566" s="2"/>
       <c r="D566" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>765</v>
+        <v>1146</v>
       </c>
       <c r="C567" s="2"/>
       <c r="D567" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C568" s="2"/>
       <c r="D568" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E568" s="2"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>769</v>
+        <v>1150</v>
       </c>
       <c r="C569" s="2"/>
       <c r="D569" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E569" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="E569" s="2"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>771</v>
+        <v>1152</v>
       </c>
       <c r="C570" s="2"/>
       <c r="D570" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E570" s="2"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C571" s="2"/>
       <c r="D571" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E571" s="2"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C572" s="2"/>
       <c r="D572" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E572" s="2"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C573" s="2"/>
       <c r="D573" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E573" s="2"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1156</v>
+        <v>771</v>
       </c>
       <c r="C574" s="2"/>
       <c r="D574" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>92</v>
@@ -11389,14 +11431,14 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1158</v>
+        <v>773</v>
       </c>
       <c r="C575" s="2"/>
       <c r="D575" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>92</v>
@@ -11404,40 +11446,42 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C576" s="2"/>
       <c r="D576" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E576" s="2"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1162</v>
+        <v>777</v>
       </c>
       <c r="C577" s="2"/>
       <c r="D577" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E577" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="E577" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1164</v>
+        <v>779</v>
       </c>
       <c r="C578" s="2"/>
       <c r="D578" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E578" s="2"/>
     </row>
@@ -11450,9 +11494,117 @@
       </c>
       <c r="C579" s="2"/>
       <c r="D579" s="2" t="s">
-        <v>1049</v>
+        <v>1065</v>
       </c>
       <c r="E579" s="2"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C580" s="2"/>
+      <c r="D580" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E580" s="2"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C581" s="2"/>
+      <c r="D581" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E581" s="2"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C582" s="2"/>
+      <c r="D582" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E582" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C583" s="2"/>
+      <c r="D583" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E583" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C584" s="2"/>
+      <c r="D584" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E584" s="2"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C585" s="2"/>
+      <c r="D585" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E585" s="2"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C586" s="2"/>
+      <c r="D586" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E586" s="2"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C587" s="2"/>
+      <c r="D587" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E587" s="2"/>
     </row>
   </sheetData>
 </worksheet>
